--- a/Compititor's_Price/IKO_Prices/IKO_Prices_17-04-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_17-04-2026.xlsx
@@ -498,17 +498,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£13.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£31.77</t>
+          <t>£32.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£47.76</t>
+          <t>£48.52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
